--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,6 +1170,52 @@
         <v>-10723</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B33" t="n">
+        <v>186695</v>
+      </c>
+      <c r="C33" t="n">
+        <v>61883</v>
+      </c>
+      <c r="D33" t="n">
+        <v>117089</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-16546</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5630</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-10916</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B34" t="n">
+        <v>184247</v>
+      </c>
+      <c r="C34" t="n">
+        <v>62656</v>
+      </c>
+      <c r="D34" t="n">
+        <v>113841</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-16519</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4277</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-12242</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1079,7 +1091,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1102,7 +1114,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1125,7 +1137,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1148,7 +1160,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1171,7 +1183,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1194,7 +1206,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,44 +421,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1160,7 +1148,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,6 +1228,29 @@
         <v>-12242</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B35" t="n">
+        <v>178724</v>
+      </c>
+      <c r="C35" t="n">
+        <v>60676</v>
+      </c>
+      <c r="D35" t="n">
+        <v>110280</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-16528</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4242</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-12286</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,44 +421,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1160,7 +1148,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1079,7 +1091,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1102,7 +1114,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1125,7 +1137,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1148,7 +1160,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1171,7 +1183,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1194,7 +1206,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1217,7 +1229,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,48 +417,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1160,7 +1148,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1249,6 +1237,29 @@
       </c>
       <c r="G35" t="n">
         <v>-12286</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B36" t="n">
+        <v>174405</v>
+      </c>
+      <c r="C36" t="n">
+        <v>55087</v>
+      </c>
+      <c r="D36" t="n">
+        <v>111597</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-16478</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3775</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-12703</v>
       </c>
     </row>
   </sheetData>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1079,7 +1091,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1102,7 +1114,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1125,7 +1137,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1148,7 +1160,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1171,7 +1183,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1194,7 +1206,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1217,7 +1229,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1240,7 +1252,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="B36" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,44 +421,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1160,7 +1148,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1252,7 +1240,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B36" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,6 +1262,29 @@
         <v>-12703</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B37" t="n">
+        <v>171204</v>
+      </c>
+      <c r="C37" t="n">
+        <v>53879</v>
+      </c>
+      <c r="D37" t="n">
+        <v>109640</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-17232</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3748</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-13484</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1079,7 +1091,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1102,7 +1114,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1125,7 +1137,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1148,7 +1160,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1171,7 +1183,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1194,7 +1206,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1217,7 +1229,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1240,7 +1252,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="B36" t="n">
@@ -1263,7 +1275,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46290</v>
       </c>
       <c r="B37" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,44 +421,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1160,7 +1148,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1252,7 +1240,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B36" t="n">
@@ -1275,7 +1263,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="B37" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,48 +417,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1160,7 +1148,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1252,7 +1240,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B36" t="n">
@@ -1275,7 +1263,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="B37" t="n">
@@ -1295,6 +1283,52 @@
       </c>
       <c r="G37" t="n">
         <v>-13484</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B38" t="n">
+        <v>166069</v>
+      </c>
+      <c r="C38" t="n">
+        <v>51323</v>
+      </c>
+      <c r="D38" t="n">
+        <v>107093</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-20150</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3532</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-16618</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B39" t="n">
+        <v>167388</v>
+      </c>
+      <c r="C39" t="n">
+        <v>52657</v>
+      </c>
+      <c r="D39" t="n">
+        <v>107062</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-19340</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3407</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-15933</v>
       </c>
     </row>
   </sheetData>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1331,6 +1331,29 @@
         <v>-15933</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B40" t="n">
+        <v>171575</v>
+      </c>
+      <c r="C40" t="n">
+        <v>56922</v>
+      </c>
+      <c r="D40" t="n">
+        <v>107008</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-16473</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2954</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-13519</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1079,7 +1091,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1102,7 +1114,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1125,7 +1137,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1148,7 +1160,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1171,7 +1183,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1194,7 +1206,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1217,7 +1229,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1240,7 +1252,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="B36" t="n">
@@ -1263,7 +1275,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46290</v>
       </c>
       <c r="B37" t="n">
@@ -1286,7 +1298,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B38" t="n">
@@ -1309,7 +1321,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46297</v>
       </c>
       <c r="B39" t="n">
@@ -1332,7 +1344,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46304</v>
       </c>
       <c r="B40" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,44 +421,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1160,7 +1148,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1252,7 +1240,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B36" t="n">
@@ -1275,7 +1263,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="B37" t="n">
@@ -1298,7 +1286,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B38" t="n">
@@ -1321,7 +1309,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>46297</v>
       </c>
       <c r="B39" t="n">
@@ -1344,7 +1332,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>46304</v>
       </c>
       <c r="B40" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,6 +1354,29 @@
         <v>-13519</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B41" t="n">
+        <v>169096</v>
+      </c>
+      <c r="C41" t="n">
+        <v>54492</v>
+      </c>
+      <c r="D41" t="n">
+        <v>106949</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-16482</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4312</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-12170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1079,7 +1091,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1102,7 +1114,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1125,7 +1137,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1148,7 +1160,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1171,7 +1183,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1194,7 +1206,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1217,7 +1229,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1240,7 +1252,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="B36" t="n">
@@ -1263,7 +1275,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>46290</v>
       </c>
       <c r="B37" t="n">
@@ -1286,7 +1298,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B38" t="n">
@@ -1309,7 +1321,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46297</v>
       </c>
       <c r="B39" t="n">
@@ -1332,7 +1344,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46304</v>
       </c>
       <c r="B40" t="n">
@@ -1355,7 +1367,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>46311</v>
       </c>
       <c r="B41" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,44 +421,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">
@@ -1160,7 +1148,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>46262</v>
       </c>
       <c r="B32" t="n">
@@ -1183,7 +1171,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B33" t="n">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>46269</v>
       </c>
       <c r="B34" t="n">
@@ -1229,7 +1217,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="B35" t="n">
@@ -1252,7 +1240,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="B36" t="n">
@@ -1275,7 +1263,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="B37" t="n">
@@ -1298,7 +1286,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B38" t="n">
@@ -1321,7 +1309,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>46297</v>
       </c>
       <c r="B39" t="n">
@@ -1344,7 +1332,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>46304</v>
       </c>
       <c r="B40" t="n">
@@ -1367,7 +1355,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>46311</v>
       </c>
       <c r="B41" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,6 +1377,29 @@
         <v>-12170</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B42" t="n">
+        <v>162191</v>
+      </c>
+      <c r="C42" t="n">
+        <v>51376</v>
+      </c>
+      <c r="D42" t="n">
+        <v>103146</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-16489</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4382</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-12107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
